--- a/03_Outputs/Turistica_Agroecologica/05_Economia/economia.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/05_Economia/economia.xlsx
@@ -22,6 +22,21 @@
     <sheet name="energia_centrales" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="energia_participacion" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="titulos_mineros" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_01" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_02" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_03" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_04" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_05" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_fig_06" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_fig_07" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_fig_08" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="_fig_09" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="_fig_10" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="_fig_11" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="_fig_12" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="_fig_13" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="_fig_14" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="_fig_15" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
 </workbook>
 </file>
@@ -4546,10 +4561,10 @@
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
     <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
     <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="61.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="65.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="67.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="66.711"/>
     <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
     <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
     <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
@@ -4586,22 +4601,22 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Valor agregado total (miles de millones $)</t>
+          <t>Valor agregado total (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades primarias (miles de millones $)</t>
+          <t>VA actividades primarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades secundarias (miles de millones $)</t>
+          <t>VA actividades secundarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>VA actividades terciarias (miles de millones $)</t>
+          <t>VA actividades terciarias (miles de millones $ constantes de 2015)</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -14688,6 +14703,326 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_nbi_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.199531438614562</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0515367635270576</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0360692946088776</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.160961517596263</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0985737210232798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.153335614881146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.103773707666453</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_pob_ipm_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0857401216192148</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.120132310655406</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0542892534374142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.0740687000544486</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.114905543880374</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.142889082918603</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0723041197646654</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_hog_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_gini_lab_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.398581702625274</v>
+      </c>
+      <c r="C2">
+        <v>0.219193735098773</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.437417092682807</v>
+      </c>
+      <c r="C3">
+        <v>0.406110121529767</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.463105024005957</v>
+      </c>
+      <c r="C4">
+        <v>0.367027363001883</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.332767454991661</v>
+      </c>
+      <c r="C5">
+        <v>0.333225297238568</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.430622321155068</v>
+      </c>
+      <c r="C6">
+        <v>0.39835041926051</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.439392388286064</v>
+      </c>
+      <c r="C7">
+        <v>0.356853884467678</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.565070665301783</v>
+      </c>
+      <c r="C8">
+        <v>0.516037796706123</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:E13"/>
@@ -14952,6 +15287,1345 @@
       </c>
       <c r="E13" s="11">
         <v>0.000351767364516267</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_to_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_emp_informal_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.57511298410298</v>
+      </c>
+      <c r="C2">
+        <v>0.577089157471963</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.414031455979954</v>
+      </c>
+      <c r="C3">
+        <v>0.662440285784677</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.576836145869068</v>
+      </c>
+      <c r="C4">
+        <v>0.654195261279913</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.461717444800055</v>
+      </c>
+      <c r="C5">
+        <v>0.694842633300909</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.499788594891951</v>
+      </c>
+      <c r="C6">
+        <v>0.652437844944005</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.539286714221316</v>
+      </c>
+      <c r="C7">
+        <v>0.857792166330973</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.482058670800447</v>
+      </c>
+      <c r="C8">
+        <v>0.539521603463488</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_mun</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>tot_td_15_28_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0518148027633202</v>
+      </c>
+      <c r="C2">
+        <v>0.0584177774755169</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0140776603803743</v>
+      </c>
+      <c r="C3">
+        <v>0.0218957072889657</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0181157076193404</v>
+      </c>
+      <c r="C4">
+        <v>0.0444598982138225</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.0753516892725542</v>
+      </c>
+      <c r="C5">
+        <v>0.231419818859883</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0525176531477479</v>
+      </c>
+      <c r="C6">
+        <v>0.0439707855119988</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.03741752625626</v>
+      </c>
+      <c r="C7">
+        <v>0.00730231587732109</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.126708595357683</v>
+      </c>
+      <c r="C8">
+        <v>0.112753120054788</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tot_nini_mun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.134976137448298</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.290116561437591</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.26864066054758</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.294687189672294</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.213737201365188</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.32201907878626</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.224221163088006</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>57.9399812441388</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>56.0415659739004</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>58.4965590259397</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>49.84375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>61.3680154142582</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>61.4835711915035</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>46.8653284994252</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>dens_emp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>24.6851387023926</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19.2716121673584</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>24.4109172821045</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>20.2393531799316</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>17.9222354888916</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>15.8465385437012</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>27.9203319549561</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>poblacion</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>va_pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>1313.72090184599</v>
+      </c>
+      <c r="D2">
+        <v>10017</v>
+      </c>
+      <c r="E2">
+        <v>131149136.65229</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>261.238509186394</v>
+      </c>
+      <c r="D3">
+        <v>12820</v>
+      </c>
+      <c r="E3">
+        <v>20377418.8132912</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>50.9289693713904</v>
+      </c>
+      <c r="D4">
+        <v>5963</v>
+      </c>
+      <c r="E4">
+        <v>8540830.01364924</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>59.85628437049</v>
+      </c>
+      <c r="D5">
+        <v>5716</v>
+      </c>
+      <c r="E5">
+        <v>10471708.25236</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>42.8458012916962</v>
+      </c>
+      <c r="D6">
+        <v>3327</v>
+      </c>
+      <c r="E6">
+        <v>12878208.9845796</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>82.2594236692017</v>
+      </c>
+      <c r="D7">
+        <v>9668</v>
+      </c>
+      <c r="E7">
+        <v>8508421.97654134</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>221.469659829869</v>
+      </c>
+      <c r="D8">
+        <v>16499</v>
+      </c>
+      <c r="E8">
+        <v>13423217.1543651</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>va_total</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>prop_va_prov</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2">
+        <v>1313.72090184599</v>
+      </c>
+      <c r="D2">
+        <v>0.646414537579565</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3">
+        <v>261.238509186394</v>
+      </c>
+      <c r="D3">
+        <v>0.12854204411029</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2024</v>
+      </c>
+      <c r="C4">
+        <v>50.9289693713904</v>
+      </c>
+      <c r="D4">
+        <v>0.0250595283513808</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2024</v>
+      </c>
+      <c r="C5">
+        <v>59.85628437049</v>
+      </c>
+      <c r="D5">
+        <v>0.0294522012462562</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2024</v>
+      </c>
+      <c r="C6">
+        <v>42.8458012916962</v>
+      </c>
+      <c r="D6">
+        <v>0.021082216770914</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>82.2594236692017</v>
+      </c>
+      <c r="D7">
+        <v>0.0404756346937701</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2024</v>
+      </c>
+      <c r="C8">
+        <v>221.469659829869</v>
+      </c>
+      <c r="D8">
+        <v>0.108973837247823</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Primarias</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Secundarias</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Terciarias</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>No distribuido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.570100376143569</v>
+      </c>
+      <c r="C2">
+        <v>0.00380444261539413</v>
+      </c>
+      <c r="D2">
+        <v>0.0554163157141646</v>
+      </c>
+      <c r="E2">
+        <v>0.370678865526872</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.409315089262786</v>
+      </c>
+      <c r="C3">
+        <v>0.0485009720636851</v>
+      </c>
+      <c r="D3">
+        <v>0.366394693605543</v>
+      </c>
+      <c r="E3">
+        <v>0.175789245067985</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0878775395889818</v>
+      </c>
+      <c r="C4">
+        <v>0.0453350943574268</v>
+      </c>
+      <c r="D4">
+        <v>0.856135695106296</v>
+      </c>
+      <c r="E4">
+        <v>0.0106516709472949</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.195463338372881</v>
+      </c>
+      <c r="C5">
+        <v>0.052368906306386</v>
+      </c>
+      <c r="D5">
+        <v>0.689077968830679</v>
+      </c>
+      <c r="E5">
+        <v>0.0630897864900537</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.199337832802183</v>
+      </c>
+      <c r="C6">
+        <v>0.0493312650839659</v>
+      </c>
+      <c r="D6">
+        <v>0.674088752013497</v>
+      </c>
+      <c r="E6">
+        <v>0.0772421501003543</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.133626301720412</v>
+      </c>
+      <c r="C7">
+        <v>0.0524777938807068</v>
+      </c>
+      <c r="D7">
+        <v>0.799401580031609</v>
+      </c>
+      <c r="E7">
+        <v>0.014494324367272</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0768508474031219</v>
+      </c>
+      <c r="C8">
+        <v>0.0494960158472663</v>
+      </c>
+      <c r="D8">
+        <v>0.849286448067439</v>
+      </c>
+      <c r="E8">
+        <v>0.0243666886821733</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>actividad</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Agricultura, ganadería, caza, silvicultura y pesca</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>176.442290796031</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Explotación de minas y canteras</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>732.160465409153</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Industrias manufactureras</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>17.1568656465539</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>23.3096119332526</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Suministro de electricidad, gas y agua</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>25.6533698558587</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Comercio, transporte y alojamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>122.340022403592</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Información y comunicaciones</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>22.2557333842059</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Actividades financieras y de seguros</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>17.6430877424004</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Actividades inmobiliarias</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>82.312949024921</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actividades profesionales, científicas y técnicas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>101.942001933393</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Administración pública, educación y salud</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>121.634781672793</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Actividades artísticas y de entretenimiento</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>42.3151519477405</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>mineral</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>n_titulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Arenas</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Minerales de oro y sus concentrados</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gravas</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recebo</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Minerales de platino y sus concentrados</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arenas siliceas</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mineral de oro</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mineral de platino</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arenas arcillosas</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Arenas feldespáticas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Otros minerales</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -15473,6 +17147,632 @@
       </c>
       <c r="J11" s="23">
         <v>0.153620919392402</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>visitantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>2019</v>
+      </c>
+      <c r="C2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2020</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2021</v>
+      </c>
+      <c r="C4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2022</v>
+      </c>
+      <c r="C5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2023</v>
+      </c>
+      <c r="C6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2024</v>
+      </c>
+      <c r="C7">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="C8">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2019</v>
+      </c>
+      <c r="C9">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2020</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2021</v>
+      </c>
+      <c r="C11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2022</v>
+      </c>
+      <c r="C12">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2025</v>
+      </c>
+      <c r="C15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2019</v>
+      </c>
+      <c r="C16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2020</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2021</v>
+      </c>
+      <c r="C18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2019</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2020</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2021</v>
+      </c>
+      <c r="C25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2022</v>
+      </c>
+      <c r="C26">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2023</v>
+      </c>
+      <c r="C27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2024</v>
+      </c>
+      <c r="C28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2019</v>
+      </c>
+      <c r="C30">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2020</v>
+      </c>
+      <c r="C31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2021</v>
+      </c>
+      <c r="C32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2022</v>
+      </c>
+      <c r="C33">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2023</v>
+      </c>
+      <c r="C34">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2024</v>
+      </c>
+      <c r="C35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Otros municipios</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2025</v>
+      </c>
+      <c r="C36">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>total_provincia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_antioquia</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>participacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2">
+        <v>205</v>
+      </c>
+      <c r="C2">
+        <v>438530</v>
+      </c>
+      <c r="D2">
+        <v>0.000467470868583677</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3">
+        <v>103</v>
+      </c>
+      <c r="C3">
+        <v>145209</v>
+      </c>
+      <c r="D3">
+        <v>0.000709322424918566</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4">
+        <v>220</v>
+      </c>
+      <c r="C4">
+        <v>303516</v>
+      </c>
+      <c r="D4">
+        <v>0.0007248382292861</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5">
+        <v>370</v>
+      </c>
+      <c r="C5">
+        <v>710194</v>
+      </c>
+      <c r="D5">
+        <v>0.000520984407077503</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6">
+        <v>259</v>
+      </c>
+      <c r="C6">
+        <v>532516</v>
+      </c>
+      <c r="D6">
+        <v>0.000486370362580655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7">
+        <v>369</v>
+      </c>
+      <c r="C7">
+        <v>905451</v>
+      </c>
+      <c r="D7">
+        <v>0.000407531716238648</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8">
+        <v>524</v>
+      </c>
+      <c r="C8">
+        <v>1038940</v>
+      </c>
+      <c r="D8">
+        <v>0.000504360213294319</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Turistica_Agroecologica/05_Economia/economia.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/05_Economia/economia.xlsx
@@ -8930,7 +8930,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
     <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
     <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
     <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
     <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
@@ -9112,10 +9112,8 @@
       <c r="F3" s="118">
         <v>21.3306304152199</v>
       </c>
-      <c r="G3" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G3" s="120">
+        <v>0.0298413546800001</v>
       </c>
       <c r="H3" s="122">
         <v>5.70826334542001</v>
@@ -9471,7 +9469,7 @@
         <v>81.4700117040194</v>
       </c>
       <c r="G9" s="121">
-        <v>13.8380668322401</v>
+        <v>13.8679081869201</v>
       </c>
       <c r="H9" s="123">
         <v>17.23011364766</v>
@@ -9765,10 +9763,8 @@
       <c r="F14" s="118">
         <v>4.48016517742484</v>
       </c>
-      <c r="G14" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G14" s="120">
+        <v>0.00880137515678552</v>
       </c>
       <c r="H14" s="122">
         <v>0.60864746421023</v>
@@ -9947,7 +9943,7 @@
         <v>107.698297463488</v>
       </c>
       <c r="G17" s="121">
-        <v>34.4604644084257</v>
+        <v>34.4692657835825</v>
       </c>
       <c r="H17" s="123">
         <v>15.2285476586181</v>
@@ -10182,10 +10178,8 @@
       <c r="F21" s="118">
         <v>16.3293645184205</v>
       </c>
-      <c r="G21" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G21" s="120">
+        <v>0.0637458040508958</v>
       </c>
       <c r="H21" s="122">
         <v>1.37565000918913</v>
@@ -10243,10 +10237,8 @@
       <c r="F22" s="118">
         <v>5.41561392511718</v>
       </c>
-      <c r="G22" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G22" s="120">
+        <v>0.0153866255718432</v>
       </c>
       <c r="H22" s="122">
         <v>0.5597772429406</v>
@@ -10425,7 +10417,7 @@
         <v>164.161035794397</v>
       </c>
       <c r="G25" s="121">
-        <v>18.6263244375499</v>
+        <v>18.7054568671727</v>
       </c>
       <c r="H25" s="123">
         <v>21.8431696574219</v>
@@ -11193,10 +11185,8 @@
       <c r="F38" s="118">
         <v>5.00234142315746</v>
       </c>
-      <c r="G38" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G38" s="120">
+        <v>0.000807663359963881</v>
       </c>
       <c r="H38" s="122">
         <v>0.125821755227523</v>
@@ -11375,7 +11365,7 @@
         <v>151.058025049365</v>
       </c>
       <c r="G41" s="121">
-        <v>7.57417900513699</v>
+        <v>7.57498666849695</v>
       </c>
       <c r="H41" s="123">
         <v>20.7073035639546</v>
@@ -11610,10 +11600,8 @@
       <c r="F45" s="118">
         <v>25.2355471600546</v>
       </c>
-      <c r="G45" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G45" s="120">
+        <v>0.0107123862475721</v>
       </c>
       <c r="H45" s="122">
         <v>2.64196335987459</v>
@@ -11671,10 +11659,8 @@
       <c r="F46" s="118">
         <v>5.68574146973354</v>
       </c>
-      <c r="G46" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G46" s="120">
+        <v>0.00229069559541647</v>
       </c>
       <c r="H46" s="122">
         <v>0.25798468973074</v>
@@ -11732,10 +11718,8 @@
       <c r="F47" s="118">
         <v>12.5342158942862</v>
       </c>
-      <c r="G47" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G47" s="120">
+        <v>0.0109582470766245</v>
       </c>
       <c r="H47" s="122">
         <v>0.822560112323682</v>
@@ -11855,7 +11839,7 @@
         <v>146.841275314384</v>
       </c>
       <c r="G49" s="121">
-        <v>180.781012149941</v>
+        <v>180.80497347886</v>
       </c>
       <c r="H49" s="123">
         <v>17.0861179836037</v>
@@ -12090,10 +12074,8 @@
       <c r="F53" s="118">
         <v>14.6032649961821</v>
       </c>
-      <c r="G53" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G53" s="120">
+        <v>0.000011474533051587</v>
       </c>
       <c r="H53" s="122">
         <v>2.43042115906235</v>
@@ -12331,7 +12313,7 @@
         <v>174.474609556005</v>
       </c>
       <c r="G57" s="121">
-        <v>411.022475908795</v>
+        <v>411.022487383328</v>
       </c>
       <c r="H57" s="123">
         <v>25.7578850357102</v>
@@ -12395,10 +12377,8 @@
       <c r="H58" s="122">
         <v>4.65005309299168</v>
       </c>
-      <c r="I58" s="124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I58" s="124">
+        <v>0.0871121736027207</v>
       </c>
       <c r="J58" s="126">
         <v>8.95543452542667</v>
@@ -12568,10 +12548,8 @@
       <c r="F61" s="118">
         <v>13.057442343982</v>
       </c>
-      <c r="G61" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G61" s="120">
+        <v>0.00420982598268679</v>
       </c>
       <c r="H61" s="122">
         <v>1.11560623028705</v>
@@ -12809,13 +12787,13 @@
         <v>159.261414841396</v>
       </c>
       <c r="G65" s="121">
-        <v>681.832129483184</v>
+        <v>681.836339309167</v>
       </c>
       <c r="H65" s="123">
         <v>18.4046883320852</v>
       </c>
       <c r="I65" s="125">
-        <v>23.9511564362386</v>
+        <v>24.0382686098413</v>
       </c>
       <c r="J65" s="127">
         <v>26.5079329399079</v>
@@ -12873,10 +12851,8 @@
       <c r="H66" s="122">
         <v>4.8083779437846</v>
       </c>
-      <c r="I66" s="124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I66" s="124">
+        <v>0.0315294998576565</v>
       </c>
       <c r="J66" s="126">
         <v>10.6130620269055</v>
@@ -12928,10 +12904,8 @@
       <c r="F67" s="118">
         <v>100.706645887152</v>
       </c>
-      <c r="G67" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G67" s="120">
+        <v>0.0168962958883971</v>
       </c>
       <c r="H67" s="122">
         <v>6.76715743247152</v>
@@ -13287,13 +13261,13 @@
         <v>157.422377029211</v>
       </c>
       <c r="G73" s="121">
-        <v>752.028747065922</v>
+        <v>752.045643361811</v>
       </c>
       <c r="H73" s="123">
         <v>18.4500018232962</v>
       </c>
       <c r="I73" s="125">
-        <v>22.4435155670656</v>
+        <v>22.4750450669232</v>
       </c>
       <c r="J73" s="127">
         <v>30.6990849977639</v>
@@ -13351,10 +13325,8 @@
       <c r="H74" s="122">
         <v>4.96038170983187</v>
       </c>
-      <c r="I74" s="124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I74" s="124">
+        <v>0.0375940738850294</v>
       </c>
       <c r="J74" s="126">
         <v>7.79695213524844</v>
@@ -13406,10 +13378,8 @@
       <c r="F75" s="118">
         <v>106.927173487956</v>
       </c>
-      <c r="G75" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G75" s="120">
+        <v>0.00169021854974549</v>
       </c>
       <c r="H75" s="122">
         <v>6.07000963541156</v>
@@ -13526,10 +13496,8 @@
       <c r="F77" s="118">
         <v>11.6943471322653</v>
       </c>
-      <c r="G77" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G77" s="120">
+        <v>0.00536203338714607</v>
       </c>
       <c r="H77" s="122">
         <v>1.13557276569901</v>
@@ -13767,13 +13735,13 @@
         <v>176.442290796031</v>
       </c>
       <c r="G81" s="121">
-        <v>732.160465409153</v>
+        <v>732.16751766109</v>
       </c>
       <c r="H81" s="123">
         <v>17.1568656465539</v>
       </c>
       <c r="I81" s="125">
-        <v>23.3096119332526</v>
+        <v>23.3472060071377</v>
       </c>
       <c r="J81" s="127">
         <v>25.6533698558587</v>
@@ -16387,7 +16355,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>732.160465409153</v>
+        <v>732.16751766109</v>
       </c>
     </row>
     <row r="4">
@@ -16407,7 +16375,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>23.3096119332526</v>
+        <v>23.3472060071377</v>
       </c>
     </row>
     <row r="6">
